--- a/artfynd/A 40736-2024 artfynd.xlsx
+++ b/artfynd/A 40736-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115983523</v>
+        <v>115983421</v>
       </c>
       <c r="B2" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533263</v>
+        <v>533502</v>
       </c>
       <c r="R2" t="n">
-        <v>7237552</v>
+        <v>7237621</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115983626</v>
+        <v>115983523</v>
       </c>
       <c r="B3" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533297</v>
+        <v>533263</v>
       </c>
       <c r="R3" t="n">
-        <v>7237468</v>
+        <v>7237552</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115983429</v>
+        <v>115983482</v>
       </c>
       <c r="B4" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533478</v>
+        <v>533565</v>
       </c>
       <c r="R4" t="n">
-        <v>7237610</v>
+        <v>7237573</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115983421</v>
+        <v>115983526</v>
       </c>
       <c r="B5" t="n">
-        <v>78589</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533502</v>
+        <v>533266</v>
       </c>
       <c r="R5" t="n">
-        <v>7237621</v>
+        <v>7237551</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,7 +1077,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115983562</v>
+        <v>115983626</v>
       </c>
       <c r="B6" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>533254</v>
+        <v>533297</v>
       </c>
       <c r="R6" t="n">
-        <v>7237518</v>
+        <v>7237468</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1230,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115983526</v>
+        <v>115983429</v>
       </c>
       <c r="B7" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>533266</v>
+        <v>533478</v>
       </c>
       <c r="R7" t="n">
-        <v>7237551</v>
+        <v>7237610</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1319,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1341,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115983482</v>
+        <v>115983530</v>
       </c>
       <c r="B8" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533565</v>
+        <v>533607</v>
       </c>
       <c r="R8" t="n">
-        <v>7237573</v>
+        <v>7237550</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1430,7 +1395,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1445,117 +1410,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>115983530</v>
-      </c>
-      <c r="B9" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Sclerophora coniophaea</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>533607</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7237550</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-09-13</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>6310</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Erik Edvardsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
